--- a/exports/QuantLab_Report.xlsx
+++ b/exports/QuantLab_Report.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:53:00 PM</t>
+          <t>12:53:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:55:00 AM</t>
+          <t>09:55:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:19:00 AM</t>
+          <t>11:19:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:14:00 AM</t>
+          <t>10:14:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:52:00 AM</t>
+          <t>10:52:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2:09:00 PM</t>
+          <t>14:09:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:50:00 AM</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:16:00 PM</t>
+          <t>12:16:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:15:00 AM</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:44:00 PM</t>
+          <t>13:44:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:20:00 AM</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:21:00 AM</t>
+          <t>10:21:00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:28:00 AM</t>
+          <t>10:28:00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:22:00 AM</t>
+          <t>10:22:00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:49:00 AM</t>
+          <t>09:49:00</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:08:00 PM</t>
+          <t>13:08:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:45:00 AM</t>
+          <t>10:45:00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:05:00 PM</t>
+          <t>12:05:00</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2:51:00 PM</t>
+          <t>14:51:00</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:29:00 AM</t>
+          <t>11:29:00</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:31:00 PM</t>
+          <t>12:31:00</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:47:00 AM</t>
+          <t>11:47:00</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:50:00 AM</t>
+          <t>11:50:00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:50:00 AM</t>
+          <t>10:50:00</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:48:00 AM</t>
+          <t>09:48:00</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:46:00 AM</t>
+          <t>09:46:00</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:10:00 PM</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:29:00 AM</t>
+          <t>11:29:00</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:57:00 AM</t>
+          <t>09:57:00</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:06:00 AM</t>
+          <t>10:06:00</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:06:00 PM</t>
+          <t>13:06:00</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:08:00 AM</t>
+          <t>11:08:00</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:18:00 AM</t>
+          <t>10:18:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:30:00 AM</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:46:00 PM</t>
+          <t>13:46:00</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:40:00 PM</t>
+          <t>13:40:00</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:25:00 AM</t>
+          <t>10:25:00</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:35:00 AM</t>
+          <t>11:35:00</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:34:00 AM</t>
+          <t>10:34:00</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:47:00 AM</t>
+          <t>10:47:00</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:43:00 AM</t>
+          <t>10:43:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:34:00 AM</t>
+          <t>11:34:00</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:53:00 AM</t>
+          <t>09:53:00</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:11:00 AM</t>
+          <t>10:11:00</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:13:00 PM</t>
+          <t>15:13:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:58:00 PM</t>
+          <t>12:58:00</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2:49:00 PM</t>
+          <t>14:49:00</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:16:00 PM</t>
+          <t>13:16:00</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:16:00 AM</t>
+          <t>10:16:00</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:05:00 AM</t>
+          <t>11:05:00</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:19:00 AM</t>
+          <t>11:19:00</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:15:00 AM</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:20:00 PM</t>
+          <t>13:20:00</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:05:00 PM</t>
+          <t>15:05:00</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:31:00 AM</t>
+          <t>10:31:00</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6799,7 +6799,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:04:00 AM</t>
+          <t>11:04:00</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:01:00 PM</t>
+          <t>12:01:00</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:35:00 AM</t>
+          <t>10:35:00</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:15:00 PM</t>
+          <t>13:15:00</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:46:00 AM</t>
+          <t>10:46:00</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:13:00 AM</t>
+          <t>10:13:00</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:53:00 AM</t>
+          <t>10:53:00</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:32:00 PM</t>
+          <t>12:32:00</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:24:00 AM</t>
+          <t>10:24:00</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:01:00 AM</t>
+          <t>11:01:00</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:35:00 AM</t>
+          <t>10:35:00</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2:02:00 PM</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:10:00 AM</t>
+          <t>10:10:00</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:22:00 AM</t>
+          <t>11:22:00</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:15:00 AM</t>
+          <t>11:15:00</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:21:00 AM</t>
+          <t>11:21:00</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:37:00 PM</t>
+          <t>12:37:00</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:54:00 AM</t>
+          <t>09:54:00</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:17:00 AM</t>
+          <t>10:17:00</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:02:00 AM</t>
+          <t>11:02:00</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:50:00 AM</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:59:00 AM</t>
+          <t>09:59:00</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:55:00 AM</t>
+          <t>09:55:00</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -9135,7 +9135,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:06:00 PM</t>
+          <t>12:06:00</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:55:00 AM</t>
+          <t>10:55:00</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:02:00 PM</t>
+          <t>12:02:00</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:07:00 AM</t>
+          <t>10:07:00</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:16:00 PM</t>
+          <t>13:16:00</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:57:00 AM</t>
+          <t>09:57:00</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:45:00 AM</t>
+          <t>10:45:00</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:49:00 AM</t>
+          <t>09:49:00</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:05:00 AM</t>
+          <t>10:05:00</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:10:00 AM</t>
+          <t>10:10:00</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:00:00 AM</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:03:00 AM</t>
+          <t>10:03:00</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:19:00 AM</t>
+          <t>10:19:00</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:05:00 AM</t>
+          <t>10:05:00</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:55:00 AM</t>
+          <t>09:55:00</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:16:00 AM</t>
+          <t>10:16:00</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -10716,7 +10716,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:13:00 PM</t>
+          <t>12:13:00</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:58:00 AM</t>
+          <t>09:58:00</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:49:00 AM</t>
+          <t>09:49:00</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:52:00 PM</t>
+          <t>13:52:00</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11124,7 +11124,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:03:00 AM</t>
+          <t>11:03:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11379,7 +11379,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:56:00 AM</t>
+          <t>09:56:00</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:54:00 AM</t>
+          <t>09:54:00</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:20:00 AM</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:48:00 AM</t>
+          <t>09:48:00</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:26:00 AM</t>
+          <t>10:26:00</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:04:00 AM</t>
+          <t>10:04:00</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:32:00 PM</t>
+          <t>13:32:00</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:45:00 AM</t>
+          <t>10:45:00</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:49:00 AM</t>
+          <t>10:49:00</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:06:00 AM</t>
+          <t>10:06:00</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -12348,7 +12348,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:33:00 AM</t>
+          <t>10:33:00</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:09:00 AM</t>
+          <t>10:09:00</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:08:00 AM</t>
+          <t>10:08:00</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -12562,7 +12562,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:32:00 AM</t>
+          <t>10:32:00</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:52:00 AM</t>
+          <t>09:52:00</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -12705,7 +12705,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:55:00 AM</t>
+          <t>09:55:00</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -12919,7 +12919,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:15:00 AM</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -12970,7 +12970,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:08:00 AM</t>
+          <t>10:08:00</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:54:00 AM</t>
+          <t>09:54:00</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:03:00 AM</t>
+          <t>11:03:00</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:53:00 AM</t>
+          <t>09:53:00</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:10:00 AM</t>
+          <t>10:10:00</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:19:00 AM</t>
+          <t>10:19:00</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:10:00 AM</t>
+          <t>10:10:00</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -13929,7 +13929,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:09:00 AM</t>
+          <t>10:09:00</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -14041,7 +14041,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:50:00 AM</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -14133,7 +14133,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2:48:00 PM</t>
+          <t>14:48:00</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -14184,7 +14184,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:56:00 AM</t>
+          <t>09:56:00</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -14235,7 +14235,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:42:00 AM</t>
+          <t>10:42:00</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:06:00 AM</t>
+          <t>10:06:00</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:49:00 AM</t>
+          <t>09:49:00</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:27:00 PM</t>
+          <t>13:27:00</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -14490,7 +14490,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:07:00 AM</t>
+          <t>11:07:00</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:13:00 AM</t>
+          <t>10:13:00</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:32:00 AM</t>
+          <t>10:32:00</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2:54:00 PM</t>
+          <t>14:54:00</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -14796,7 +14796,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:43:00 AM</t>
+          <t>11:43:00</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:16:00 AM</t>
+          <t>10:16:00</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:02:00 PM</t>
+          <t>13:02:00</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:57:00 AM</t>
+          <t>09:57:00</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -15163,7 +15163,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:47:00 AM</t>
+          <t>09:47:00</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -15255,7 +15255,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:57:00 AM</t>
+          <t>11:57:00</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:15:00 PM</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -15520,7 +15520,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:54:00 AM</t>
+          <t>09:54:00</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -15561,7 +15561,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 2:02:00 PM</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -15673,7 +15673,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -15724,7 +15724,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:10:00 AM</t>
+          <t>10:10:00</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -15765,7 +15765,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -15775,7 +15775,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:58:00 AM</t>
+          <t>09:58:00</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -15867,7 +15867,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:59:00 AM</t>
+          <t>09:59:00</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -15969,7 +15969,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -15979,7 +15979,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -16020,7 +16020,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -16081,7 +16081,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:01:00 AM</t>
+          <t>10:01:00</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -16183,7 +16183,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:52:00 AM</t>
+          <t>09:52:00</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:07:00 PM</t>
+          <t>12:07:00</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -16336,7 +16336,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -16377,7 +16377,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -16428,7 +16428,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:42:00 AM</t>
+          <t>10:42:00</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:12:00 AM</t>
+          <t>10:12:00</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:20:00 PM</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:10:00 AM</t>
+          <t>10:10:00</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -16693,7 +16693,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:54:00 AM</t>
+          <t>09:54:00</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -16795,7 +16795,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:31:00 AM</t>
+          <t>10:31:00</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -16948,7 +16948,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:57:00 AM</t>
+          <t>09:57:00</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1:09:00 PM</t>
+          <t>13:09:00</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -17050,7 +17050,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:00:00 AM</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:15:00 AM</t>
+          <t>10:15:00</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -17193,7 +17193,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:47:00 AM</t>
+          <t>10:47:00</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -17244,7 +17244,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:50:00 AM</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -17356,7 +17356,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:16:00 AM</t>
+          <t>10:16:00</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -17448,7 +17448,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -17509,7 +17509,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:06:00 AM</t>
+          <t>10:06:00</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:04:00 PM</t>
+          <t>12:04:00</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -17713,7 +17713,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:46:00 AM</t>
+          <t>09:46:00</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:54:00 AM</t>
+          <t>09:54:00</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -17856,7 +17856,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:02:00 AM</t>
+          <t>11:02:00</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -18009,7 +18009,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:03:00 PM</t>
+          <t>15:03:00</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -18111,7 +18111,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:58:00 AM</t>
+          <t>09:58:00</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:35:00 AM</t>
+          <t>10:35:00</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -18223,7 +18223,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:53:00 AM</t>
+          <t>09:53:00</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:01:00 AM</t>
+          <t>10:01:00</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -18376,7 +18376,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:34:00 PM</t>
+          <t>12:34:00</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -18417,7 +18417,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -18478,7 +18478,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:50:00 AM</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -18519,7 +18519,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -18529,7 +18529,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -18580,7 +18580,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:47:00 AM</t>
+          <t>10:47:00</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -18672,7 +18672,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -18733,7 +18733,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12:33:00 PM</t>
+          <t>12:33:00</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -18784,7 +18784,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -18825,7 +18825,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:10:00 AM</t>
+          <t>10:10:00</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -18876,7 +18876,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -18927,7 +18927,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -18937,7 +18937,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:19:00 AM</t>
+          <t>10:19:00</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -18978,7 +18978,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -19029,7 +19029,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:58:00 AM</t>
+          <t>09:58:00</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -19141,7 +19141,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:56:00 AM</t>
+          <t>09:56:00</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:46:00 AM</t>
+          <t>09:46:00</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -19284,7 +19284,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:50:00 AM</t>
+          <t>09:50:00</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -19447,7 +19447,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:58:00 AM</t>
+          <t>09:58:00</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -19498,7 +19498,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:49:00 AM</t>
+          <t>09:49:00</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -19590,7 +19590,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -19600,7 +19600,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:16:00 AM</t>
+          <t>10:16:00</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:48:00 AM</t>
+          <t>09:48:00</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -19702,7 +19702,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:57:00 AM</t>
+          <t>11:57:00</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -19804,7 +19804,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:46:00 AM</t>
+          <t>09:46:00</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:22:00 AM</t>
+          <t>10:22:00</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -19896,7 +19896,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -19906,7 +19906,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:46:00 AM</t>
+          <t>09:46:00</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -19957,7 +19957,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -19998,7 +19998,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -20110,7 +20110,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -20151,7 +20151,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -20161,7 +20161,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -20202,7 +20202,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -20212,7 +20212,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:56:00 AM</t>
+          <t>09:56:00</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -20304,7 +20304,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10:49:00 AM</t>
+          <t>10:49:00</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -20365,7 +20365,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3:27:00 PM</t>
+          <t>15:27:00</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -20406,7 +20406,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 9:44:00 AM</t>
+          <t>09:44:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -20416,7 +20416,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11:13:00 AM</t>
+          <t>11:13:00</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">

--- a/exports/QuantLab_Report.xlsx
+++ b/exports/QuantLab_Report.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Monthly" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Weekly" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Weekday" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Duration" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64086,4 +64087,407 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Duration Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Duration Bucket</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Trades</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Losses</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Gross Loss</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Avg P&amp;L</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Best Trade</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Worst Trade</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Profit Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0-15 min</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>121497.22</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-121497.22</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-2429.9444</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-2102.78</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-3189.55</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15-30 min</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>29</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>74227.74000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-74227.74000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-2559.577241379311</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-2079.53</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-4116.87</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30-60 min</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>36</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>87898.33</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-87898.33</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2441.620277777778</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-2071.91</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-4413.44</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>78864.06999999999</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-78864.06999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-2389.820303030303</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-2051.03</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-4177.73</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>85762.44</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-85762.44</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-2522.424705882353</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-2088.24</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-5203.57</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>204</v>
+      </c>
+      <c r="C9" t="n">
+        <v>187</v>
+      </c>
+      <c r="D9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" t="n">
+        <v>91.66666666666666</v>
+      </c>
+      <c r="F9" t="n">
+        <v>758695.64</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30755.44</v>
+      </c>
+      <c r="H9" t="n">
+        <v>727940.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3568.33431372549</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15938.81</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-3611.17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>24.66866479556137</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6+ hrs Same Day</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Overnight / Multi-day</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/exports/QuantLab_Report.xlsx
+++ b/exports/QuantLab_Report.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Weekly" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Weekday" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Duration" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Streak" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -64490,4 +64491,2926 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C229"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Streak Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Longest Winning Streak</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Longest Losing Streak</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Average Winning Streak</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Average Losing Streak</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Total Winning Streaks</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Total Losing Streaks</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Current Streak Type</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Current Streak Length</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Largest Winning Streak P&amp;L</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>33423.18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Largest Losing Streak P&amp;L</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-18117.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Streak Type</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1284.97</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-2326.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5579.13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-2200.75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>7312.38</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-13807.33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4545.86</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-2166.68</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2644.59</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-2223.47</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6860.96</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-4554.34</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7082.06</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-2112.32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>6306.16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-5177.03</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3535.55</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-2107.22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>6945.01</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-2083.62</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2835.69</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-2427.94</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3590.03</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-4264.32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3312.17</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-4227.29</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" t="n">
+        <v>6411.46</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-2500.66</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>556.11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-2803.27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>6987.69</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-4939.78</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>9730.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-10063.71</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>6730.59</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-4490.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="n">
+        <v>9027.41</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-13995.08</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5165.94</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-2094.84</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" t="n">
+        <v>10388.91</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-2388.9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>7584.49</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-6625.04</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2998.68</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-4713.68</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2</v>
+      </c>
+      <c r="C62" t="n">
+        <v>8423.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-2135.67</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3237.93</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-6757.52</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>5847.33</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-2245.78</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" t="n">
+        <v>6492.44</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-2694.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9212.459999999999</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-2284.78</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="n">
+        <v>18609.53</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-2218.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3278.76</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-4582.27</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>4</v>
+      </c>
+      <c r="C76" t="n">
+        <v>13776.12</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-9717.639999999999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="n">
+        <v>6304.2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-10608.35</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>6763.97</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>4</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-8843.950000000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>7315.35</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-2120.35</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>5</v>
+      </c>
+      <c r="C84" t="n">
+        <v>28254.05</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-6864.96</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>6</v>
+      </c>
+      <c r="C86" t="n">
+        <v>18489.37</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-2963.19</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>5602.61</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-4778.15</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2</v>
+      </c>
+      <c r="C90" t="n">
+        <v>18660.85</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-7000.61</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4253.15</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-2301.75</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4818.6</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-8610.66</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="n">
+        <v>11408.43</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>3</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-9719.74</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>9143.129999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-2465.27</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2</v>
+      </c>
+      <c r="C100" t="n">
+        <v>7235.78</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-6815.42</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C102" t="n">
+        <v>9121.49</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-2124.56</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>6409.59</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-2313.29</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>4</v>
+      </c>
+      <c r="C106" t="n">
+        <v>22767.38</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-2149.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3986.47</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-2320.34</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>2690.94</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-2242.84</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2</v>
+      </c>
+      <c r="C112" t="n">
+        <v>5889.66</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-2235.07</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2710.53</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-2161.88</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4917.3</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-5145.55</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2</v>
+      </c>
+      <c r="C118" t="n">
+        <v>10047.97</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-2797.83</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2</v>
+      </c>
+      <c r="C120" t="n">
+        <v>10103.73</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-2162.83</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="n">
+        <v>3898.37</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-2298.45</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" t="n">
+        <v>9121.08</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-8798.51</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4392.03</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>3</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-6330.35</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4163.51</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-842.38</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2</v>
+      </c>
+      <c r="C130" t="n">
+        <v>7861.13</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-2259.48</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="n">
+        <v>4074.46</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>4</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-9089.6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="n">
+        <v>5721.97</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-2102.78</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>3</v>
+      </c>
+      <c r="C136" t="n">
+        <v>12471.37</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-4584.32</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2</v>
+      </c>
+      <c r="C138" t="n">
+        <v>7423.68</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-2217.52</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3639.18</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-2247.9</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>3</v>
+      </c>
+      <c r="C142" t="n">
+        <v>8677.190000000001</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-4177.73</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" t="n">
+        <v>4260.68</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-5901.57</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3485.37</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-2208.07</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3501.19</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-2295.23</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="n">
+        <v>6125.24</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-3691.22</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="n">
+        <v>7084.24</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>3</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-7658.64</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3648.56</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>8</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-18117.88</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="n">
+        <v>8598.83</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-4990.32</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="n">
+        <v>7412.91</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-4413.44</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4030.59</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>2</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-4886.63</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>2</v>
+      </c>
+      <c r="C162" t="n">
+        <v>5908.56</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-4699.89</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="n">
+        <v>4916.15</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-3062.9</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>2</v>
+      </c>
+      <c r="C166" t="n">
+        <v>5465.83</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-3032.83</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" t="n">
+        <v>4446.5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-3611.17</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" t="n">
+        <v>4790.83</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-3325.79</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="n">
+        <v>10830.66</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-2173.05</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="n">
+        <v>4919.38</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-2285.12</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>2</v>
+      </c>
+      <c r="C176" t="n">
+        <v>10395.63</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>4</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-9088.92</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3</v>
+      </c>
+      <c r="C178" t="n">
+        <v>9652.24</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>2</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-4593.39</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="n">
+        <v>550.84</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>2</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-6654.84</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="n">
+        <v>6200.45</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-2306.62</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2</v>
+      </c>
+      <c r="C184" t="n">
+        <v>5677.34</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>5</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-12030.77</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="n">
+        <v>5959.62</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-2307.06</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2755.14</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-2216.5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2917.8</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-2504.01</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3348.48</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-6147.41</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2</v>
+      </c>
+      <c r="C194" t="n">
+        <v>10789.27</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>2</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-4910.33</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>3</v>
+      </c>
+      <c r="C196" t="n">
+        <v>12937.69</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>2</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-4609.28</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2926.09</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>3</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-6704.73</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1930.35</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>2</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-5211.96</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="n">
+        <v>4511.05</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="n">
+        <v>-2111.64</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="n">
+        <v>5126.47</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="n">
+        <v>-2294.83</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2</v>
+      </c>
+      <c r="C206" t="n">
+        <v>12962.46</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="n">
+        <v>-2896.89</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="n">
+        <v>4656.18</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>-2445.9</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="n">
+        <v>4826.9</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="n">
+        <v>-3079.29</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="n">
+        <v>4173.47</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="n">
+        <v>-2544.38</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3056.67</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>2</v>
+      </c>
+      <c r="C215" t="n">
+        <v>-4772.52</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>2</v>
+      </c>
+      <c r="C216" t="n">
+        <v>10882.44</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="n">
+        <v>-2349.34</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="n">
+        <v>4412.64</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2</v>
+      </c>
+      <c r="C219" t="n">
+        <v>-4935.27</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" t="n">
+        <v>8159.55</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>3</v>
+      </c>
+      <c r="C221" t="n">
+        <v>-9096.17</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="n">
+        <v>15938.81</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>3</v>
+      </c>
+      <c r="C223" t="n">
+        <v>-8998</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>5</v>
+      </c>
+      <c r="C224" t="n">
+        <v>33423.18</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" t="n">
+        <v>-2340.41</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1261.28</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" t="n">
+        <v>-2596.36</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Win</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" t="n">
+        <v>5205.15</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" t="n">
+        <v>-2279.27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/exports/QuantLab_Report.xlsx
+++ b/exports/QuantLab_Report.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Duration" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Streak" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Calendar" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Risk" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17241,6 +17242,137 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Risk Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Standard Deviation</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3617.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Downside Deviation</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>583.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Sharpe Ratio</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Sortino Ratio</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.242</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Calmar Ratio</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>16.167</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Ulcer Index</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.539</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Recovery Factor</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Value at Risk (95%)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-3062.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Conditional VaR (95%)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-3611.34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Kelly %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>17.86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Half Kelly %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8.93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
